--- a/data/trans_orig/IP2907_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2907_2023-Edad-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5940</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14224</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7715</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17109</t>
+          <t>16751</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15707</t>
+          <t>15845</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28365</t>
+          <t>28459</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,69%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32786</t>
+          <t>32683</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41070</t>
+          <t>41182</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28613</t>
+          <t>28971</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38007</t>
+          <t>38128</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64367</t>
+          <t>64273</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77025</t>
+          <t>76887</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,91%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21582</t>
+          <t>21898</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37153</t>
+          <t>37737</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26360</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45160</t>
+          <t>45255</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52883</t>
+          <t>53263</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76938</t>
+          <t>76995</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>120899</t>
+          <t>120315</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>136470</t>
+          <t>136154</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135888</t>
+          <t>135793</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>154688</t>
+          <t>153965</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>262162</t>
+          <t>262105</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>286217</t>
+          <t>285837</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24155</t>
+          <t>24255</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42488</t>
+          <t>42242</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31320</t>
+          <t>30817</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53950</t>
+          <t>54153</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61162</t>
+          <t>60774</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90975</t>
+          <t>88445</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>129040</t>
+          <t>129286</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>147373</t>
+          <t>147273</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158540</t>
+          <t>158337</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181170</t>
+          <t>181673</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>293043</t>
+          <t>295573</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>322856</t>
+          <t>323244</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37045</t>
+          <t>36818</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58182</t>
+          <t>57682</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43744</t>
+          <t>42935</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80314</t>
+          <t>78172</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86574</t>
+          <t>87444</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126222</t>
+          <t>126343</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>182237</t>
+          <t>182737</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203374</t>
+          <t>203601</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>217706</t>
+          <t>219848</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>254276</t>
+          <t>255085</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>412217</t>
+          <t>412096</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>451865</t>
+          <t>450995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,76%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>100877</t>
+          <t>100103</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132963</t>
+          <t>135554</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>125043</t>
+          <t>126570</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>172695</t>
+          <t>171111</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>237069</t>
+          <t>236214</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>295702</t>
+          <t>290681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>484046</t>
+          <t>481455</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>516132</t>
+          <t>516906</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>564585</t>
+          <t>566169</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>612237</t>
+          <t>610710</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1058587</t>
+          <t>1063608</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1117220</t>
+          <t>1118075</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,56%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2907_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2907_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9195</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13434</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>24,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15,48%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>35,53%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9605</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5828</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14327</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20,43%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,4%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11811</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16751</t>
+          <t>13613</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>21417</t>
+          <t>18118</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>13186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28459</t>
+          <t>24360</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,14%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28615</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24376</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>31956</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>75,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>64,47%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>84,52%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>37405</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>32683</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>41182</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>79,57%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>69,52%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>87,6%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33911</t>
+          <t>34093</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28971</t>
+          <t>29404</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38128</t>
+          <t>37176</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>71315</t>
+          <t>62709</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64273</t>
+          <t>56467</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76887</t>
+          <t>67641</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37810</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37810</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37810</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>47010</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>47010</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>47010</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45722</t>
+          <t>43017</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45722</t>
+          <t>43017</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45722</t>
+          <t>43017</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>92732</t>
+          <t>80827</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>92732</t>
+          <t>80827</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>92732</t>
+          <t>80827</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>29283</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>21740</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37796</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18,73%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,91%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24,18%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>28983</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>21898</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>37737</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>18,34%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13,86%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34883</t>
+          <t>25585</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27083</t>
+          <t>19674</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45255</t>
+          <t>32705</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>63867</t>
+          <t>54868</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53263</t>
+          <t>45188</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76995</t>
+          <t>65957</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>127018</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>118505</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>134561</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,27%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>75,82%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,09%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>129069</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>120315</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>136154</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>81,66%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>76,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>86,14%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>146165</t>
+          <t>118704</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135793</t>
+          <t>111584</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>153965</t>
+          <t>124615</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>275233</t>
+          <t>245722</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>262105</t>
+          <t>234633</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>285837</t>
+          <t>255402</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,97%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156301</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156301</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156301</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>158052</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>158052</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>158052</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181048</t>
+          <t>144289</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181048</t>
+          <t>144289</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181048</t>
+          <t>144289</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>339100</t>
+          <t>300590</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>339100</t>
+          <t>300590</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>339100</t>
+          <t>300590</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>39667</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30258</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>50343</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19,82%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,16%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>32801</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>24255</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>42242</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,12%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,14%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>41293</t>
+          <t>34052</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30817</t>
+          <t>25593</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54153</t>
+          <t>44882</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>74094</t>
+          <t>73719</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60774</t>
+          <t>61622</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88445</t>
+          <t>89460</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>160459</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>149783</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>169868</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>80,18%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>74,84%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>138727</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>129286</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>147273</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>80,88%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,37%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,86%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>171197</t>
+          <t>139054</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158337</t>
+          <t>128224</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181673</t>
+          <t>147513</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>309924</t>
+          <t>299513</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>295573</t>
+          <t>283772</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>323244</t>
+          <t>311610</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>83,49%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>171528</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>171528</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>171528</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173106</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173106</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173106</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>384018</t>
+          <t>373232</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>384018</t>
+          <t>373232</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>384018</t>
+          <t>373232</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>52605</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>40335</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>69274</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,14%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24,28%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>46035</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>36818</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>57682</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>19,15%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15,31%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,99%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57920</t>
+          <t>47644</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42935</t>
+          <t>36698</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78172</t>
+          <t>58400</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>103955</t>
+          <t>100248</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87444</t>
+          <t>83489</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126343</t>
+          <t>119390</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>232739</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>216070</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>245009</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>75,72%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,86%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>194384</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>182737</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>203601</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>80,85%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>76,01%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>84,69%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>240100</t>
+          <t>197043</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>219848</t>
+          <t>186287</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>255085</t>
+          <t>207989</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>434484</t>
+          <t>429783</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>412096</t>
+          <t>410641</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>450995</t>
+          <t>446542</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,25%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>285344</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>285344</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>285344</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>240419</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>240419</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>240419</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>298020</t>
+          <t>244687</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>298020</t>
+          <t>244687</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>298020</t>
+          <t>244687</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>538439</t>
+          <t>530031</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>538439</t>
+          <t>530031</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>538439</t>
+          <t>530031</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>130749</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>111678</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>150256</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,24%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>16,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>22,11%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>117425</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>100103</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>135554</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>19,03%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>16,22%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,97%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>145907</t>
+          <t>116205</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>126570</t>
+          <t>101842</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>171111</t>
+          <t>133829</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>263332</t>
+          <t>246954</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>236214</t>
+          <t>223274</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>290681</t>
+          <t>276884</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>548832</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>529325</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>567903</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>80,76%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>77,89%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>83,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>726</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>499584</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>481455</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>516906</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>80,97%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>78,03%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>83,78%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>591373</t>
+          <t>488895</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>566169</t>
+          <t>471271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>610710</t>
+          <t>503258</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1090957</t>
+          <t>1037727</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1063608</t>
+          <t>1007797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1118075</t>
+          <t>1061407</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,62%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>679581</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>679581</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>679581</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>904</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>617009</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>617009</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>617009</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>737280</t>
+          <t>605100</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>737280</t>
+          <t>605100</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>737280</t>
+          <t>605100</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1354289</t>
+          <t>1284681</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1354289</t>
+          <t>1284681</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1354289</t>
+          <t>1284681</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
